--- a/data/trans_orig/P11_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P11_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2007</t>
+          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56169</t>
+          <t>57485</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88692</t>
+          <t>89343</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54506</t>
+          <t>54699</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83781</t>
+          <t>83974</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>118390</t>
+          <t>118250</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159919</t>
+          <t>163226</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>385084</t>
+          <t>384433</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>417607</t>
+          <t>416291</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>222899</t>
+          <t>222706</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>252174</t>
+          <t>251981</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>620538</t>
+          <t>617231</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>662067</t>
+          <t>662207</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,85%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32268</t>
+          <t>31644</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57229</t>
+          <t>56663</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53936</t>
+          <t>53318</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82919</t>
+          <t>82792</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94895</t>
+          <t>93905</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>134736</t>
+          <t>134173</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>309705</t>
+          <t>310271</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>334666</t>
+          <t>335290</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>288946</t>
+          <t>289073</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>317929</t>
+          <t>318547</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>604063</t>
+          <t>604626</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>643904</t>
+          <t>644894</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,29%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82178</t>
+          <t>82838</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>118359</t>
+          <t>117382</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37706</t>
+          <t>39297</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62103</t>
+          <t>63102</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>127786</t>
+          <t>127687</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>172690</t>
+          <t>172228</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,25%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>424030</t>
+          <t>425007</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>460211</t>
+          <t>459551</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>105679</t>
+          <t>104680</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130076</t>
+          <t>128485</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>537481</t>
+          <t>537943</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>582385</t>
+          <t>582484</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,02%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>253245</t>
+          <t>252281</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>313496</t>
+          <t>314403</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>164845</t>
+          <t>164891</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>210686</t>
+          <t>213001</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>435980</t>
+          <t>435330</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>508813</t>
+          <t>509237</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,08%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>924838</t>
+          <t>923931</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>985089</t>
+          <t>986053</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>503599</t>
+          <t>501284</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>549440</t>
+          <t>549394</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1443807</t>
+          <t>1443383</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1516640</t>
+          <t>1517290</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,71%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61412</t>
+          <t>62752</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93056</t>
+          <t>93783</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>142329</t>
+          <t>143118</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>186277</t>
+          <t>186500</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>212436</t>
+          <t>212515</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>266931</t>
+          <t>266439</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>257499</t>
+          <t>256772</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>289143</t>
+          <t>287803</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>382475</t>
+          <t>382252</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>426423</t>
+          <t>425634</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>652376</t>
+          <t>652868</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>706871</t>
+          <t>706792</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,88%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>12988</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30409</t>
+          <t>29957</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>413067</t>
+          <t>416188</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>482107</t>
+          <t>484368</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>435294</t>
+          <t>436605</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>506592</t>
+          <t>506072</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,71%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>267792</t>
+          <t>268244</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>284892</t>
+          <t>285213</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>766653</t>
+          <t>764392</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>835693</t>
+          <t>832572</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1040368</t>
+          <t>1040888</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1111666</t>
+          <t>1110355</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,78%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>555562</t>
+          <t>554380</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>645566</t>
+          <t>638869</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>936804</t>
+          <t>926587</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1039619</t>
+          <t>1041082</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1509474</t>
+          <t>1513361</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1653787</t>
+          <t>1655783</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2624624</t>
+          <t>2631321</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2714628</t>
+          <t>2715810</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2338505</t>
+          <t>2337042</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2441320</t>
+          <t>2451537</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4994527</t>
+          <t>4992531</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5138840</t>
+          <t>5134953</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,24%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2012</t>
+          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40017</t>
+          <t>39412</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68621</t>
+          <t>67613</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39643</t>
+          <t>38915</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66071</t>
+          <t>66588</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>87659</t>
+          <t>86017</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>129905</t>
+          <t>123192</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>365735</t>
+          <t>366743</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>394339</t>
+          <t>394944</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248383</t>
+          <t>247866</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>274811</t>
+          <t>275539</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>618905</t>
+          <t>625618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>661151</t>
+          <t>662793</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,51%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52861</t>
+          <t>52589</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85516</t>
+          <t>86627</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50080</t>
+          <t>49695</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80732</t>
+          <t>79499</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>110109</t>
+          <t>109517</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156357</t>
+          <t>155457</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>332281</t>
+          <t>331170</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364936</t>
+          <t>365208</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>256344</t>
+          <t>257577</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>286996</t>
+          <t>287381</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>598516</t>
+          <t>599416</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>644764</t>
+          <t>645356</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,49%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124179</t>
+          <t>124072</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>171680</t>
+          <t>169311</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67940</t>
+          <t>67922</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>100788</t>
+          <t>100519</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>200276</t>
+          <t>199058</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>255046</t>
+          <t>257260</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>453620</t>
+          <t>455989</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>501121</t>
+          <t>501228</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158369</t>
+          <t>158638</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>191217</t>
+          <t>191235</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>629411</t>
+          <t>627197</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>684181</t>
+          <t>685399</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,49%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>228329</t>
+          <t>227434</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>286192</t>
+          <t>283660</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>168392</t>
+          <t>165692</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>219784</t>
+          <t>215049</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>409465</t>
+          <t>410360</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>489101</t>
+          <t>490031</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>868954</t>
+          <t>871486</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>926817</t>
+          <t>927712</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>545854</t>
+          <t>550589</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>597246</t>
+          <t>599946</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1431683</t>
+          <t>1430753</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1511319</t>
+          <t>1510424</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,64%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83353</t>
+          <t>83987</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>120566</t>
+          <t>119375</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>267705</t>
+          <t>270089</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>326943</t>
+          <t>324381</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>365541</t>
+          <t>365156</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>432070</t>
+          <t>432244</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,09%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>386624</t>
+          <t>387815</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>423837</t>
+          <t>423203</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>433640</t>
+          <t>436202</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>492878</t>
+          <t>490494</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>835703</t>
+          <t>835529</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>902232</t>
+          <t>902617</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,2%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11302</t>
+          <t>12096</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30829</t>
+          <t>29875</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>387627</t>
+          <t>389190</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>453724</t>
+          <t>454118</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>404224</t>
+          <t>401938</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>475281</t>
+          <t>473251</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,43%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>234200</t>
+          <t>235154</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>253727</t>
+          <t>252933</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>655627</t>
+          <t>655233</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>721724</t>
+          <t>720161</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>899100</t>
+          <t>901130</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>970157</t>
+          <t>972443</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,75%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>591475</t>
+          <t>599608</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>691674</t>
+          <t>696043</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1051414</t>
+          <t>1055887</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1161993</t>
+          <t>1163511</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1671036</t>
+          <t>1675644</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1825052</t>
+          <t>1822749</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2713144</t>
+          <t>2708775</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2813343</t>
+          <t>2805210</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2384267</t>
+          <t>2382749</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2494846</t>
+          <t>2490373</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5126026</t>
+          <t>5128329</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5280042</t>
+          <t>5275434</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,89%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2016</t>
+          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2016 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48156</t>
+          <t>48434</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77698</t>
+          <t>78335</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47268</t>
+          <t>47564</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76062</t>
+          <t>76593</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102595</t>
+          <t>101035</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>145587</t>
+          <t>142400</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>346621</t>
+          <t>345984</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>376163</t>
+          <t>375885</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>268214</t>
+          <t>267683</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>297008</t>
+          <t>296712</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>623008</t>
+          <t>626195</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>666000</t>
+          <t>667560</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33937</t>
+          <t>34577</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60534</t>
+          <t>60411</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56370</t>
+          <t>57328</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>87726</t>
+          <t>88524</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>98077</t>
+          <t>98149</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>140607</t>
+          <t>137895</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>315710</t>
+          <t>315833</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>342307</t>
+          <t>341667</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>282631</t>
+          <t>281833</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313987</t>
+          <t>313029</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>605994</t>
+          <t>608706</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>648524</t>
+          <t>648452</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86660</t>
+          <t>87755</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>126238</t>
+          <t>124145</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35141</t>
+          <t>35757</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58814</t>
+          <t>60560</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>131322</t>
+          <t>130667</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>176856</t>
+          <t>175579</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>391925</t>
+          <t>394018</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>431503</t>
+          <t>430408</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>105141</t>
+          <t>103395</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128814</t>
+          <t>128198</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>505262</t>
+          <t>506539</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>550796</t>
+          <t>551451</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,84%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>219735</t>
+          <t>222873</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>278681</t>
+          <t>279088</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>177863</t>
+          <t>177406</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>228049</t>
+          <t>227974</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>418843</t>
+          <t>416247</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>495475</t>
+          <t>492802</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,12%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>862823</t>
+          <t>862416</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>921769</t>
+          <t>918631</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>591864</t>
+          <t>591939</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>642050</t>
+          <t>642507</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1465942</t>
+          <t>1468615</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1542574</t>
+          <t>1545170</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,78%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>126769</t>
+          <t>125159</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>169088</t>
+          <t>167378</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>235363</t>
+          <t>240159</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>289979</t>
+          <t>292354</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>376189</t>
+          <t>376571</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>442963</t>
+          <t>446864</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>448303</t>
+          <t>450013</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>490622</t>
+          <t>492232</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>445362</t>
+          <t>442987</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>499978</t>
+          <t>495182</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>909769</t>
+          <t>905868</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>976543</t>
+          <t>976161</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,16%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>8739</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24338</t>
+          <t>24838</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>330297</t>
+          <t>330073</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>395302</t>
+          <t>394077</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>336946</t>
+          <t>342638</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>408847</t>
+          <t>410818</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259042</t>
+          <t>258542</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>274698</t>
+          <t>274641</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>679899</t>
+          <t>681124</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>744904</t>
+          <t>745128</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>949734</t>
+          <t>947763</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1021635</t>
+          <t>1015943</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>74,78%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>579636</t>
+          <t>579015</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>670721</t>
+          <t>673924</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>950118</t>
+          <t>952785</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1061366</t>
+          <t>1062509</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1559901</t>
+          <t>1560262</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1709370</t>
+          <t>1710589</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2690280</t>
+          <t>2687077</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2781365</t>
+          <t>2781986</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2447676</t>
+          <t>2446533</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2558924</t>
+          <t>2556257</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5160674</t>
+          <t>5159455</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5310143</t>
+          <t>5309782</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2023</t>
+          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91325</t>
+          <t>90925</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>124608</t>
+          <t>126274</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>107158</t>
+          <t>107293</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138939</t>
+          <t>139240</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>205799</t>
+          <t>205610</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>254228</t>
+          <t>254548</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>379189</t>
+          <t>377523</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>412472</t>
+          <t>412872</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>307237</t>
+          <t>306936</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>339018</t>
+          <t>338883</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>695745</t>
+          <t>695425</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>744174</t>
+          <t>744363</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,36%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87301</t>
+          <t>88252</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>120755</t>
+          <t>122730</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>94530</t>
+          <t>95114</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>124765</t>
+          <t>126383</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>190338</t>
+          <t>192937</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>235813</t>
+          <t>238235</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,58%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>330727</t>
+          <t>328752</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364181</t>
+          <t>363230</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>257241</t>
+          <t>255623</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>287476</t>
+          <t>286892</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>597674</t>
+          <t>595252</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>643149</t>
+          <t>640550</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>76,85%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51780</t>
+          <t>46503</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>214866</t>
+          <t>217068</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66384</t>
+          <t>66609</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87758</t>
+          <t>87450</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86125</t>
+          <t>85352</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>304228</t>
+          <t>301415</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,13%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452482</t>
+          <t>450280</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>615568</t>
+          <t>620845</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79153</t>
+          <t>79461</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>100527</t>
+          <t>100302</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>530030</t>
+          <t>532843</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>748133</t>
+          <t>748906</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,77%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>291384</t>
+          <t>289879</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>350237</t>
+          <t>351610</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>333972</t>
+          <t>332933</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>718239</t>
+          <t>675935</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>642086</t>
+          <t>641389</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1142032</t>
+          <t>1185718</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>58,91%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>684582</t>
+          <t>683209</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>743435</t>
+          <t>744940</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>259855</t>
+          <t>302159</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>644122</t>
+          <t>645161</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>870880</t>
+          <t>827194</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1370826</t>
+          <t>1371523</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,14%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>136518</t>
+          <t>139481</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>177807</t>
+          <t>180099</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>258826</t>
+          <t>265270</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>401799</t>
+          <t>399916</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>414259</t>
+          <t>411918</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>555801</t>
+          <t>554537</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,14%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>297239</t>
+          <t>294947</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>338528</t>
+          <t>335565</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>439103</t>
+          <t>440986</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>582076</t>
+          <t>575632</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>760146</t>
+          <t>761410</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>901688</t>
+          <t>904029</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,7%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14167</t>
+          <t>14368</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46432</t>
+          <t>47425</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>284771</t>
+          <t>284763</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>334328</t>
+          <t>332201</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>305192</t>
+          <t>304722</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>365826</t>
+          <t>366773</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,67%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>194075</t>
+          <t>193082</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>226340</t>
+          <t>226139</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>425444</t>
+          <t>427571</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>475001</t>
+          <t>475009</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>634453</t>
+          <t>633506</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>695087</t>
+          <t>695557</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,54%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>648153</t>
+          <t>662678</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>933385</t>
+          <t>936357</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1294954</t>
+          <t>1286358</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1868919</t>
+          <t>1851867</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2056758</t>
+          <t>2072808</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2722785</t>
+          <t>2787337</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>40,12%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2439613</t>
+          <t>2436641</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2724845</t>
+          <t>2710320</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1704941</t>
+          <t>1721993</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2278906</t>
+          <t>2287502</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4224073</t>
+          <t>4159521</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4890100</t>
+          <t>4874050</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,16%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P11_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P11_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57485</t>
+          <t>57120</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89343</t>
+          <t>88582</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54699</t>
+          <t>54910</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83974</t>
+          <t>84343</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>118250</t>
+          <t>120362</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>163226</t>
+          <t>162051</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>384433</t>
+          <t>385194</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>416291</t>
+          <t>416656</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>222706</t>
+          <t>222337</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>251981</t>
+          <t>251770</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>617231</t>
+          <t>618406</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>662207</t>
+          <t>660095</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,58%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31644</t>
+          <t>32183</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56663</t>
+          <t>57480</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53318</t>
+          <t>53343</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82792</t>
+          <t>85202</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93905</t>
+          <t>92552</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>134173</t>
+          <t>130140</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>310271</t>
+          <t>309454</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>335290</t>
+          <t>334751</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289073</t>
+          <t>286663</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>318547</t>
+          <t>318522</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>604626</t>
+          <t>608659</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>644894</t>
+          <t>646247</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,47%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82838</t>
+          <t>83688</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117382</t>
+          <t>119034</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39297</t>
+          <t>37998</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63102</t>
+          <t>62057</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>127687</t>
+          <t>129112</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>172228</t>
+          <t>170959</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>425007</t>
+          <t>423355</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>459551</t>
+          <t>458701</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>104680</t>
+          <t>105725</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128485</t>
+          <t>129784</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>537943</t>
+          <t>539212</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>582484</t>
+          <t>581059</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>81,82%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>252281</t>
+          <t>254089</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>314403</t>
+          <t>311049</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>164891</t>
+          <t>166916</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>213001</t>
+          <t>212734</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>435330</t>
+          <t>436329</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>509237</t>
+          <t>513077</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>923931</t>
+          <t>927285</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>986053</t>
+          <t>984245</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>501284</t>
+          <t>501551</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>549394</t>
+          <t>547369</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1443383</t>
+          <t>1439543</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1517290</t>
+          <t>1516291</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,65%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62752</t>
+          <t>63338</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93783</t>
+          <t>95471</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>143118</t>
+          <t>142691</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>186500</t>
+          <t>186130</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>212515</t>
+          <t>212517</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>266439</t>
+          <t>268907</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,25%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>256772</t>
+          <t>255084</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>287803</t>
+          <t>287217</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>382252</t>
+          <t>382622</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>425634</t>
+          <t>426061</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>652868</t>
+          <t>650400</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>706792</t>
+          <t>706790</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>12654</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29957</t>
+          <t>31396</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>416188</t>
+          <t>417978</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>484368</t>
+          <t>481407</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>436605</t>
+          <t>435139</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>506072</t>
+          <t>503845</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>268244</t>
+          <t>266805</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>285213</t>
+          <t>285547</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>764392</t>
+          <t>767353</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>832572</t>
+          <t>830782</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1040888</t>
+          <t>1043115</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1110355</t>
+          <t>1111821</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,87%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>554380</t>
+          <t>552396</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>638869</t>
+          <t>639100</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>926587</t>
+          <t>935909</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1041082</t>
+          <t>1041952</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1513361</t>
+          <t>1513415</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1655783</t>
+          <t>1646858</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2631321</t>
+          <t>2631090</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2715810</t>
+          <t>2717794</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2337042</t>
+          <t>2336172</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2451537</t>
+          <t>2442215</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4992531</t>
+          <t>5001456</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5134953</t>
+          <t>5134899</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39412</t>
+          <t>40821</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67613</t>
+          <t>69748</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38915</t>
+          <t>39026</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66588</t>
+          <t>67268</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>86017</t>
+          <t>85118</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>123192</t>
+          <t>125551</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>366743</t>
+          <t>364608</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>394944</t>
+          <t>393535</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>247866</t>
+          <t>247186</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275539</t>
+          <t>275428</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>625618</t>
+          <t>623259</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>662793</t>
+          <t>663692</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,63%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52589</t>
+          <t>51226</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86627</t>
+          <t>84908</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49695</t>
+          <t>48729</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79499</t>
+          <t>79981</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>109517</t>
+          <t>107246</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>155457</t>
+          <t>154792</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>331170</t>
+          <t>332889</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>365208</t>
+          <t>366571</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>257577</t>
+          <t>257095</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>287381</t>
+          <t>288347</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>599416</t>
+          <t>600081</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>645356</t>
+          <t>647627</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,79%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124072</t>
+          <t>124070</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>169311</t>
+          <t>171528</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67922</t>
+          <t>68837</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>100519</t>
+          <t>99124</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>199058</t>
+          <t>200546</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>257260</t>
+          <t>255223</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>455989</t>
+          <t>453772</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>501228</t>
+          <t>501230</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158638</t>
+          <t>160033</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>191235</t>
+          <t>190320</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>627197</t>
+          <t>629234</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>685399</t>
+          <t>683911</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>227434</t>
+          <t>227820</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>283660</t>
+          <t>286364</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>165692</t>
+          <t>166227</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>215049</t>
+          <t>213683</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>410360</t>
+          <t>411870</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>490031</t>
+          <t>485750</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>871486</t>
+          <t>868782</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>927712</t>
+          <t>927326</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>550589</t>
+          <t>551955</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>599946</t>
+          <t>599411</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1430753</t>
+          <t>1435034</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1510424</t>
+          <t>1508914</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,56%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83987</t>
+          <t>83334</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>119375</t>
+          <t>118771</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>270089</t>
+          <t>271262</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>324381</t>
+          <t>325759</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>365156</t>
+          <t>364799</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>432244</t>
+          <t>429788</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,9%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>387815</t>
+          <t>388419</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>423203</t>
+          <t>423856</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>436202</t>
+          <t>434824</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>490494</t>
+          <t>489321</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>835529</t>
+          <t>837985</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>902617</t>
+          <t>902974</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,23%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12096</t>
+          <t>12003</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29875</t>
+          <t>29254</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>389190</t>
+          <t>389502</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>454118</t>
+          <t>458857</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>401938</t>
+          <t>406074</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>473251</t>
+          <t>476710</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,69%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>235154</t>
+          <t>235775</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252933</t>
+          <t>253026</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>655233</t>
+          <t>650494</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>720161</t>
+          <t>719849</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>901130</t>
+          <t>897671</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>972443</t>
+          <t>968307</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,45%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>599608</t>
+          <t>597731</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>696043</t>
+          <t>693298</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1055887</t>
+          <t>1051975</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1163511</t>
+          <t>1163360</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1675644</t>
+          <t>1681743</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1822749</t>
+          <t>1830513</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2708775</t>
+          <t>2711520</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2805210</t>
+          <t>2807087</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2382749</t>
+          <t>2382900</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2490373</t>
+          <t>2494285</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5128329</t>
+          <t>5120565</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5275434</t>
+          <t>5269335</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,81%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48434</t>
+          <t>45691</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78335</t>
+          <t>76480</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47564</t>
+          <t>47719</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76593</t>
+          <t>77087</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101035</t>
+          <t>101389</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142400</t>
+          <t>145789</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>345984</t>
+          <t>347839</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>375885</t>
+          <t>378628</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>267683</t>
+          <t>267189</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>296712</t>
+          <t>296557</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>626195</t>
+          <t>622806</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>667560</t>
+          <t>667206</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,81%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34577</t>
+          <t>34052</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60411</t>
+          <t>60190</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57328</t>
+          <t>57319</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>88524</t>
+          <t>88614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>98149</t>
+          <t>97544</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137895</t>
+          <t>137395</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>315833</t>
+          <t>316054</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>341667</t>
+          <t>342192</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>281833</t>
+          <t>281743</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313029</t>
+          <t>313038</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>608706</t>
+          <t>609206</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>648452</t>
+          <t>649057</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,93%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87755</t>
+          <t>88044</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>124145</t>
+          <t>125747</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35757</t>
+          <t>35423</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60560</t>
+          <t>60209</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>130667</t>
+          <t>128188</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175579</t>
+          <t>175092</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>394018</t>
+          <t>392416</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>430408</t>
+          <t>430119</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>103395</t>
+          <t>103746</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128198</t>
+          <t>128532</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>506539</t>
+          <t>507026</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>551451</t>
+          <t>553930</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>81,21%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>222873</t>
+          <t>223169</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>279088</t>
+          <t>280526</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>177406</t>
+          <t>177101</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>227974</t>
+          <t>225092</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>416247</t>
+          <t>417298</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>492802</t>
+          <t>493952</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,18%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>862416</t>
+          <t>860978</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>918631</t>
+          <t>918335</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>591939</t>
+          <t>594821</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>642507</t>
+          <t>642812</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1468615</t>
+          <t>1467465</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1545170</t>
+          <t>1544119</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,72%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>125159</t>
+          <t>127929</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>167378</t>
+          <t>169245</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>240159</t>
+          <t>238637</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>292354</t>
+          <t>289958</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>376571</t>
+          <t>376003</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>446864</t>
+          <t>443580</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,79%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>450013</t>
+          <t>448146</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>492232</t>
+          <t>489462</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>442987</t>
+          <t>445383</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>495182</t>
+          <t>496704</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>905868</t>
+          <t>909152</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>976161</t>
+          <t>976729</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,2%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8739</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24838</t>
+          <t>25667</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>330073</t>
+          <t>327367</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>394077</t>
+          <t>393426</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>342638</t>
+          <t>342845</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>410818</t>
+          <t>409822</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258542</t>
+          <t>257713</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>274641</t>
+          <t>274796</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>681124</t>
+          <t>681775</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>745128</t>
+          <t>747834</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>947763</t>
+          <t>948759</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1015943</t>
+          <t>1015736</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,76%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>579015</t>
+          <t>576317</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>673924</t>
+          <t>672587</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>952785</t>
+          <t>951334</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1062509</t>
+          <t>1063959</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1560262</t>
+          <t>1557736</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1710589</t>
+          <t>1704478</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2687077</t>
+          <t>2688414</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2781986</t>
+          <t>2784684</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2446533</t>
+          <t>2445083</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2556257</t>
+          <t>2557708</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5159455</t>
+          <t>5165566</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5309782</t>
+          <t>5312308</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>106847</t>
+          <t>117577</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90925</t>
+          <t>98716</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>126274</t>
+          <t>136913</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>122427</t>
+          <t>132887</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>107293</t>
+          <t>118439</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>139240</t>
+          <t>149536</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>229274</t>
+          <t>250464</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>205610</t>
+          <t>226693</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>254548</t>
+          <t>277075</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>396950</t>
+          <t>431463</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>377523</t>
+          <t>412127</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>412872</t>
+          <t>450324</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>323749</t>
+          <t>353934</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>306936</t>
+          <t>337285</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>338883</t>
+          <t>368382</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>720699</t>
+          <t>785397</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>695425</t>
+          <t>758786</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>744363</t>
+          <t>809168</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,12%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>503797</t>
+          <t>549040</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>503797</t>
+          <t>549040</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>503797</t>
+          <t>549040</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446176</t>
+          <t>486821</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446176</t>
+          <t>486821</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446176</t>
+          <t>486821</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>949973</t>
+          <t>1035861</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>949973</t>
+          <t>1035861</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>949973</t>
+          <t>1035861</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>104162</t>
+          <t>107185</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88252</t>
+          <t>90430</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>122730</t>
+          <t>127093</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>109674</t>
+          <t>122220</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>95114</t>
+          <t>107545</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>126383</t>
+          <t>136861</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>213835</t>
+          <t>229406</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>192937</t>
+          <t>205910</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>238235</t>
+          <t>254479</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>347320</t>
+          <t>375023</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>328752</t>
+          <t>355115</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363230</t>
+          <t>391778</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>272332</t>
+          <t>300266</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>255623</t>
+          <t>285625</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>286892</t>
+          <t>314941</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>619652</t>
+          <t>675288</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>595252</t>
+          <t>650215</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>640550</t>
+          <t>698784</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,24%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451482</t>
+          <t>482208</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451482</t>
+          <t>482208</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451482</t>
+          <t>482208</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382006</t>
+          <t>422486</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382006</t>
+          <t>422486</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382006</t>
+          <t>422486</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>833487</t>
+          <t>904694</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>833487</t>
+          <t>904694</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>833487</t>
+          <t>904694</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>131308</t>
+          <t>140215</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46503</t>
+          <t>121683</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>217068</t>
+          <t>163070</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>76654</t>
+          <t>83936</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66609</t>
+          <t>72761</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87450</t>
+          <t>94866</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>207962</t>
+          <t>224151</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85352</t>
+          <t>201951</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>301415</t>
+          <t>248596</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>37,78%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>536040</t>
+          <t>330357</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>450280</t>
+          <t>307502</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>620845</t>
+          <t>348889</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>90257</t>
+          <t>103561</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79461</t>
+          <t>92631</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>100302</t>
+          <t>114736</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>626296</t>
+          <t>433918</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>532843</t>
+          <t>409473</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>748906</t>
+          <t>456118</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>69,31%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667348</t>
+          <t>470572</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667348</t>
+          <t>470572</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667348</t>
+          <t>470572</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834258</t>
+          <t>658069</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834258</t>
+          <t>658069</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834258</t>
+          <t>658069</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>319246</t>
+          <t>346116</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>289879</t>
+          <t>313766</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>351610</t>
+          <t>376687</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>476451</t>
+          <t>299358</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>332933</t>
+          <t>275771</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>675935</t>
+          <t>322263</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>795697</t>
+          <t>645475</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>641389</t>
+          <t>607697</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1185718</t>
+          <t>687530</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>715573</t>
+          <t>785727</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>683209</t>
+          <t>755156</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>744940</t>
+          <t>818077</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>501643</t>
+          <t>561853</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>302159</t>
+          <t>538948</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>645161</t>
+          <t>585440</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1217215</t>
+          <t>1347579</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>827194</t>
+          <t>1305524</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1371523</t>
+          <t>1385357</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>69,51%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>157695</t>
+          <t>179921</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139481</t>
+          <t>159810</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>180099</t>
+          <t>204819</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>351811</t>
+          <t>381372</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>265270</t>
+          <t>359584</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>399916</t>
+          <t>405838</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>509505</t>
+          <t>561293</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>411918</t>
+          <t>526942</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>554537</t>
+          <t>594130</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,49%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>317351</t>
+          <t>388043</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>294947</t>
+          <t>363145</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>335565</t>
+          <t>408154</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>489091</t>
+          <t>449012</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>440986</t>
+          <t>424546</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>575632</t>
+          <t>470800</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>806442</t>
+          <t>837055</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>761410</t>
+          <t>804218</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>904029</t>
+          <t>871406</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>62,32%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>840902</t>
+          <t>830384</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>840902</t>
+          <t>830384</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>840902</t>
+          <t>830384</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1315947</t>
+          <t>1398348</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1315947</t>
+          <t>1398348</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1315947</t>
+          <t>1398348</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>25914</t>
+          <t>25735</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14368</t>
+          <t>14474</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47425</t>
+          <t>43903</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>308612</t>
+          <t>334896</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>284763</t>
+          <t>308654</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>332201</t>
+          <t>359540</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>334526</t>
+          <t>360632</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>304722</t>
+          <t>330928</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>366773</t>
+          <t>391567</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,26%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>214593</t>
+          <t>211493</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>193082</t>
+          <t>193325</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>226139</t>
+          <t>222754</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>451160</t>
+          <t>507639</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>427571</t>
+          <t>482995</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>475009</t>
+          <t>533881</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>665753</t>
+          <t>719131</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>633506</t>
+          <t>688196</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>695557</t>
+          <t>748835</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,35%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>759772</t>
+          <t>842535</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>759772</t>
+          <t>842535</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>759772</t>
+          <t>842535</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000279</t>
+          <t>1079763</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000279</t>
+          <t>1079763</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000279</t>
+          <t>1079763</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>845172</t>
+          <t>916750</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>662678</t>
+          <t>864402</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>936357</t>
+          <t>971319</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,22 +10726,22 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1445629</t>
+          <t>1354670</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1286358</t>
+          <t>1306938</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1851867</t>
+          <t>1402808</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2290801</t>
+          <t>2271419</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2072808</t>
+          <t>2194777</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2787337</t>
+          <t>2340387</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>33,1%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2527826</t>
+          <t>2522104</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2436641</t>
+          <t>2467535</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2710320</t>
+          <t>2574452</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,27 +10839,27 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2128231</t>
+          <t>2276266</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1721993</t>
+          <t>2228128</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2287502</t>
+          <t>2323998</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4656057</t>
+          <t>4798370</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4159521</t>
+          <t>4729402</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4874050</t>
+          <t>4875012</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>68,96%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3372998</t>
+          <t>3438854</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3372998</t>
+          <t>3438854</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3372998</t>
+          <t>3438854</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3573860</t>
+          <t>3630936</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3573860</t>
+          <t>3630936</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3573860</t>
+          <t>3630936</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6946858</t>
+          <t>7069789</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6946858</t>
+          <t>7069789</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6946858</t>
+          <t>7069789</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
